--- a/telecommuting_forms/006_zoom_appointment_form--telecommuting_forms.xlsx
+++ b/telecommuting_forms/006_zoom_appointment_form--telecommuting_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>form_category_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Form Category 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>form_description_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Form Description 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>form_description_en</t>
+          <t>form_description_en_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Description (en)</t>
+          <t>Form Description En 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>form_language</t>
+          <t>form_language_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>form_id_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>form_category_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>form_description_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>form_description_en</t>
+          <t>form_description_en_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Description (en)</t>
+          <t>Form Description En 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>form_description_fr</t>
+          <t>form_description_fr_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Description (fr)</t>
+          <t>Form Description Fr 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>form_description_es</t>
+          <t>form_description_es_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Description (es)</t>
+          <t>Form Description Es 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,7 +980,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>form_language</t>
+          <t>form_language_3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>form_id_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>form_category_4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>form_description_4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Beschreibung</t>
+          <t>Form Description 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>form_description_en</t>
+          <t>form_description_en_4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Description (en)</t>
+          <t>Form Description En 4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1160,7 +1160,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>form_category_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +1177,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>form_category_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1262,7 +1262,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>form_language_choices</t>
+          <t>form_language_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +1279,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>form_language_choices</t>
+          <t>form_language_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1296,7 +1296,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>form_language_choices</t>
+          <t>form_language_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,7 +1313,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>form_language_choices</t>
+          <t>form_language_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1330,7 +1330,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>form_category_3_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1347,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>form_category_3_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,7 +1364,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>form_language_choices</t>
+          <t>form_language_3_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,7 +1381,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>form_language_choices</t>
+          <t>form_language_3_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1398,7 +1398,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>form_language_choices</t>
+          <t>form_language_3_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>form_language_choices</t>
+          <t>form_language_3_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1432,7 +1432,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>form_category_4_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1449,7 +1449,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>form_category_4_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
